--- a/outputs/Fuel_(diesel)_percentile_classification_matrix.xlsx
+++ b/outputs/Fuel_(diesel)_percentile_classification_matrix.xlsx
@@ -679,7 +679,7 @@
     <t>No data</t>
   </si>
   <si>
-    <t>Minimal</t>
+    <t>No concern</t>
   </si>
   <si>
     <t>0%</t>
